--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA334"/>
+  <dimension ref="A1:AA338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35499,6 +35499,454 @@
       <c r="Z334" s="2" t="inlineStr"/>
       <c r="AA334" s="2" t="inlineStr"/>
     </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>11515</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Popești-Leordeni</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Județul Ilfov, Oraş Popeşti Leordeni</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>215 Şoseaua Olteniţei</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>077160</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://dulciuriaugust.ro</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>officefastplus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>16324763</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr"/>
+      <c r="S335" s="2" t="inlineStr"/>
+      <c r="T335" s="2" t="inlineStr"/>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Valeriu Voluta</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/voluta-valeriu-781b55210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M336" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q336" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Elena Tanase</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>Buying Director</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-tanase-a9401166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M337" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q337" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t>Andreea Dulca</t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>Sourcing Specialist</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreea-dulca-69382787/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M338" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q338" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Tulbure Petre Daniel</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Advisory Sales Specialist / Sommelier</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tulbure-petre-daniel-b1ba9818a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA338"/>
+  <dimension ref="A1:AA342"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35947,6 +35947,454 @@
         </is>
       </c>
     </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>11515</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Popești-Leordeni</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr">
+        <is>
+          <t>Județul Ilfov, Oraş Popeşti Leordeni</t>
+        </is>
+      </c>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>215 Şoseaua Olteniţei</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>077160</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://dulciuriaugust.ro</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M339" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>officefastplus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr"/>
+      <c r="P339" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q339" s="2" t="inlineStr">
+        <is>
+          <t>16324763</t>
+        </is>
+      </c>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr"/>
+      <c r="T339" s="2" t="inlineStr"/>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Valeriu Voluta</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/voluta-valeriu-781b55210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M340" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q340" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Elena Tanase</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Buying Director</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-tanase-a9401166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M341" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q341" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Andreea Dulca</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>Sourcing Specialist</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreea-dulca-69382787/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Tulbure Petre Daniel</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Advisory Sales Specialist / Sommelier</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tulbure-petre-daniel-b1ba9818a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA342"/>
+  <dimension ref="A1:AA346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36395,6 +36395,454 @@
         </is>
       </c>
     </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>11515</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Popești-Leordeni</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Ilfov</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>215 Şoseaua Olteniţei</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>077160</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://dulciuriaugust.ro</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>officefastplus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr"/>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>16324763</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr"/>
+      <c r="S343" s="2" t="inlineStr"/>
+      <c r="T343" s="2" t="inlineStr"/>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr"/>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Valeriu Voluta</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/voluta-valeriu-781b55210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W344" s="2" t="inlineStr">
+        <is>
+          <t>Elena Tanase</t>
+        </is>
+      </c>
+      <c r="X344" s="2" t="inlineStr">
+        <is>
+          <t>Buying Director</t>
+        </is>
+      </c>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-tanase-a9401166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>Andreea Dulca</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Sourcing Specialist</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreea-dulca-69382787/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Tulbure Petre Daniel</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Advisory Sales Specialist / Sommelier</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tulbure-petre-daniel-b1ba9818a/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA346"/>
+  <dimension ref="A1:AA350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36843,6 +36843,454 @@
         </is>
       </c>
     </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Fast Plus Srl</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>11515</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Popești-Leordeni</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Ilfov</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>215 Şoseaua Olteniţei</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>077160</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://dulciuriaugust.ro</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>officefastplus@gmail.com</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr"/>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>16324763</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr"/>
+      <c r="S347" s="2" t="inlineStr"/>
+      <c r="T347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Valeriu Voluta</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/voluta-valeriu-781b55210/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>Tulbure Petre Daniel</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>Advisory Sales Specialist / Sommelier</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tulbure-petre-daniel-b1ba9818a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>Elena Tanase</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>Buying Director</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elena-tanase-a9401166/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Mega Image Srl</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>11536</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>26 Bulevardul Timișoara</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>061344</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.mega-image.ro</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>10317</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>relatii_clienti@mega-image.ro</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 224 6677</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>6719278</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mega-image-s-r-l-</t>
+        </is>
+      </c>
+      <c r="S350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MegaImageRomania/</t>
+        </is>
+      </c>
+      <c r="T350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/megaimageromania</t>
+        </is>
+      </c>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCK0Yvb5w16oXk-jocqV5ZAw</t>
+        </is>
+      </c>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t>Andreea Dulca</t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>Sourcing Specialist</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreea-dulca-69382787/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA350"/>
+  <dimension ref="A1:AA353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37291,6 +37291,257 @@
         </is>
       </c>
     </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Sorla Distribution S.r.l.</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Sorla Distribution S.r.l.</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>86363</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>1 Aleea Pantelimon</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>022401</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sorla.ro</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr"/>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>contact@sorla.ro</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr"/>
+      <c r="P351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr"/>
+      <c r="R351" s="2" t="inlineStr"/>
+      <c r="S351" s="2" t="inlineStr"/>
+      <c r="T351" s="2" t="inlineStr"/>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr">
+        <is>
+          <t>Zoe Ghiuri</t>
+        </is>
+      </c>
+      <c r="X351" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Odorest Srl</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Odorest Srl</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>22656</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Odorheiu Secuiesc</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Harghita</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>53 Strada Budvár</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>535600</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.odorest.ro</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>odorest@gmail.com</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>+40 266 217 976</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>1991</t>
+        </is>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>524471</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr"/>
+      <c r="S352" s="2" t="inlineStr"/>
+      <c r="T352" s="2" t="inlineStr"/>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr"/>
+      <c r="W352" s="2" t="inlineStr"/>
+      <c r="X352" s="2" t="inlineStr"/>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik Noise Srl</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik Noise Srl</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>103000</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Iași</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Iași</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>4 Strada Bașotă</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>700082</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://tipsy.ro</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>contact@tipsy.ro</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr"/>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>36527380</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr"/>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/tipsy.ro</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tipsy.ro/</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr"/>
+      <c r="W353" s="2" t="inlineStr"/>
+      <c r="X353" s="2" t="inlineStr"/>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA353"/>
+  <dimension ref="A1:AA362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37542,6 +37542,939 @@
       <c r="Z353" s="2" t="inlineStr"/>
       <c r="AA353" s="2" t="inlineStr"/>
     </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Athanasios Group S.r.l</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Athanasios Group S.r.l</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>59796</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>143 Calea Moșilor</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>030167</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>https://iubescsivinul.ro</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>contact@iubescsivinul.ro</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr"/>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>24241740</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/iubescsivinul.ro</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iubescsivinul/</t>
+        </is>
+      </c>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr"/>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>11485</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Traian Street, No. 184-186, Et. 5, Sector 2</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>020284</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>http://www.bdg.ro</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr"/>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>office@bdg.ro</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 323 8670</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>15413099</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bdg-import/</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr"/>
+      <c r="T355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>Ionuț Cuțeică</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ionu%C8%9B-cu%C8%9Beic%C4%83-7ab84323/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>11485</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Traian Street, No. 184-186, Et. 5, Sector 2</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>020284</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>http://www.bdg.ro</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr"/>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>office@bdg.ro</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 323 8670</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>15413099</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bdg-import/</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Ana Maria Stoica</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-maria-stoica-03355328/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Bdg Import Srl</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>11485</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>Traian Street, No. 184-186, Et. 5, Sector 2</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>020284</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>http://www.bdg.ro</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr"/>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>office@bdg.ro</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>+40 21 323 8670</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>15413099</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bdg-import/</t>
+        </is>
+      </c>
+      <c r="S357" s="2" t="inlineStr"/>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>Petru Berciu</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petru-berciu-5b016a12/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>22477</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Cluj-Napoca</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Cluj</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>1-3 Calea Baciului</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>400230</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winepoint.ro</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>office@winepoint.ro</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>+40 264 449 794</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>31468770</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-point-srl/</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winepointromania/</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winepointromania</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>Ciprian Banciu</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ciprian-banciu-280609226</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>22477</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Cluj-Napoca</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Cluj</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>1-3 Calea Baciului</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>400230</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winepoint.ro</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>office@winepoint.ro</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>+40 264 449 794</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>31468770</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-point-srl/</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winepointromania/</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winepointromania</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>Adina Vulcan</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Communications Public Relations Manager</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adina-vulcan-5670529/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Wine Point Srl</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>22477</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Cluj-Napoca</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Cluj</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>1-3 Calea Baciului</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>400230</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winepoint.ro</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M360" s="2" t="inlineStr"/>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>office@winepoint.ro</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>+40 264 449 794</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q360" s="2" t="inlineStr">
+        <is>
+          <t>31468770</t>
+        </is>
+      </c>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wine-point-srl/</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winepointromania/</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winepointromania</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>Maia Banciu</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mihaela-maia-banciu-6113b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Direct Client Services Srl</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cărtureşti </t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>106496</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>15 Strada Pictor Arthur Verona</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>030167</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://carturesti.ro</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr"/>
+      <c r="M361" s="2" t="inlineStr"/>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>ecomenzi@carturesti.info</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>+40 376 448 000</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q361" s="2" t="inlineStr">
+        <is>
+          <t>11648548</t>
+        </is>
+      </c>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carturesti/</t>
+        </is>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CarturestiOnline/</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/librariile_carturesti/</t>
+        </is>
+      </c>
+      <c r="U361" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Carturestii</t>
+        </is>
+      </c>
+      <c r="V361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/CarturestiTube/</t>
+        </is>
+      </c>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>Ioana Niculescu</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ioana-niculescu-24761869/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Direct Client Services Srl</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cărtureşti </t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>106496</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>București</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>15 Strada Pictor Arthur Verona</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>030167</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>https://carturesti.ro</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr"/>
+      <c r="M362" s="2" t="inlineStr"/>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>ecomenzi@carturesti.info</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>+40 376 448 000</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>11648548</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/carturesti/</t>
+        </is>
+      </c>
+      <c r="S362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CarturestiOnline/</t>
+        </is>
+      </c>
+      <c r="T362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/librariile_carturesti/</t>
+        </is>
+      </c>
+      <c r="U362" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Carturestii</t>
+        </is>
+      </c>
+      <c r="V362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/CarturestiTube/</t>
+        </is>
+      </c>
+      <c r="W362" s="2" t="inlineStr">
+        <is>
+          <t>Nistorescu Alina</t>
+        </is>
+      </c>
+      <c r="X362" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nistorescu-alina-8a2842a9/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA362"/>
+  <dimension ref="A1:AA368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -38475,6 +38475,648 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr"/>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr"/>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Nicoleta Irina</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director / General Manager</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicoleta-irina-ro%C8%99co-b881b5149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr"/>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr"/>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>Felician Vasile Tamas</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Account Manager </t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/felician-vasile-tamas-a4b927228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr"/>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>Vasile Roșco</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/vasile-rosco-9ba98b139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr"/>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>Ana-Cristina Cioroianu-Ezaru</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>Junior Category Manager Wines Spirits</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-cristina-cioroianu-ezaru-dinu-9b87877a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr"/>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>Marian Poenaru</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-poenaru-160751272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr"/>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Alexandru</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrei-alexandru-32918922b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA368"/>
+  <dimension ref="A1:AA374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39117,6 +39117,648 @@
         </is>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr"/>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>Nicoleta Irina</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director / General Manager</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicoleta-irina-ro%C8%99co-b881b5149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr"/>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr">
+        <is>
+          <t>Felician Vasile Tamas</t>
+        </is>
+      </c>
+      <c r="X370" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Account Manager </t>
+        </is>
+      </c>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/felician-vasile-tamas-a4b927228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr"/>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr">
+        <is>
+          <t>Vasile Roșco</t>
+        </is>
+      </c>
+      <c r="X371" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/vasile-rosco-9ba98b139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr"/>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W372" s="2" t="inlineStr">
+        <is>
+          <t>Ana-Cristina Cioroianu-Ezaru</t>
+        </is>
+      </c>
+      <c r="X372" s="2" t="inlineStr">
+        <is>
+          <t>Junior Category Manager Wines Spirits</t>
+        </is>
+      </c>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-cristina-cioroianu-ezaru-dinu-9b87877a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr"/>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W373" s="2" t="inlineStr">
+        <is>
+          <t>Marian Poenaru</t>
+        </is>
+      </c>
+      <c r="X373" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-poenaru-160751272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr"/>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W374" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Alexandru</t>
+        </is>
+      </c>
+      <c r="X374" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrei-alexandru-32918922b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA374"/>
+  <dimension ref="A1:AA380"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39759,6 +39759,648 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr"/>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>Nicoleta Irina</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director / General Manager</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicoleta-irina-ro%C8%99co-b881b5149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr"/>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr"/>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>Felician Vasile Tamas</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Account Manager </t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/felician-vasile-tamas-a4b927228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr"/>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr"/>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>Vasile Roșco</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/vasile-rosco-9ba98b139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr"/>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q378" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W378" s="2" t="inlineStr">
+        <is>
+          <t>Ana-Cristina Cioroianu-Ezaru</t>
+        </is>
+      </c>
+      <c r="X378" s="2" t="inlineStr">
+        <is>
+          <t>Junior Category Manager Wines Spirits</t>
+        </is>
+      </c>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-cristina-cioroianu-ezaru-dinu-9b87877a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr"/>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Marian Poenaru</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-poenaru-160751272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr"/>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W380" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Alexandru</t>
+        </is>
+      </c>
+      <c r="X380" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrei-alexandru-32918922b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA380"/>
+  <dimension ref="A1:AA386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40401,6 +40401,648 @@
         </is>
       </c>
     </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr"/>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr">
+        <is>
+          <t>Nicoleta Irina</t>
+        </is>
+      </c>
+      <c r="X381" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director / General Manager</t>
+        </is>
+      </c>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicoleta-irina-ro%C8%99co-b881b5149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr"/>
+      <c r="P382" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q382" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr">
+        <is>
+          <t>Felician Vasile Tamas</t>
+        </is>
+      </c>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Account Manager </t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/felician-vasile-tamas-a4b927228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr"/>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>Vasile Roșco</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/vasile-rosco-9ba98b139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr"/>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W384" s="2" t="inlineStr">
+        <is>
+          <t>Ana-Cristina Cioroianu-Ezaru</t>
+        </is>
+      </c>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>Junior Category Manager Wines Spirits</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-cristina-cioroianu-ezaru-dinu-9b87877a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr"/>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W385" s="2" t="inlineStr">
+        <is>
+          <t>Marian Poenaru</t>
+        </is>
+      </c>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-poenaru-160751272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr"/>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Alexandru</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrei-alexandru-32918922b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Romania.xlsx
+++ b/BWI/bestwine_output/bestwine_Romania.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA386"/>
+  <dimension ref="A1:AA392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41043,6 +41043,648 @@
         </is>
       </c>
     </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr"/>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr">
+        <is>
+          <t>Nicoleta Irina</t>
+        </is>
+      </c>
+      <c r="X387" s="2" t="inlineStr">
+        <is>
+          <t>Executive Director / General Manager</t>
+        </is>
+      </c>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicoleta-irina-ro%C8%99co-b881b5149/</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr"/>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr"/>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr">
+        <is>
+          <t>Felician Vasile Tamas</t>
+        </is>
+      </c>
+      <c r="X388" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Key Account Manager </t>
+        </is>
+      </c>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/felician-vasile-tamas-a4b927228/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Rossell &amp; Co Srl</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>105372</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Satu Mare</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Județul Satu Mare</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>47B Strada Principală</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>447230</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.rossell.ro</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>info@rossell.ro</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr"/>
+      <c r="P389" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q389" s="2" t="inlineStr">
+        <is>
+          <t>14284948</t>
+        </is>
+      </c>
+      <c r="R389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rossell-co/</t>
+        </is>
+      </c>
+      <c r="S389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/RossellRomania/</t>
+        </is>
+      </c>
+      <c r="T389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rossell_romania/</t>
+        </is>
+      </c>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr">
+        <is>
+          <t>Vasile Roșco</t>
+        </is>
+      </c>
+      <c r="X389" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/vasile-rosco-9ba98b139/</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr"/>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Ana-Cristina Cioroianu-Ezaru</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Junior Category Manager Wines Spirits</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ana-cristina-cioroianu-ezaru-dinu-9b87877a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr"/>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Marian Poenaru</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>Regional Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marian-poenaru-160751272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Metro Cash &amp; Carry Romania Srl</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>25765</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Bucureşti</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Bucharest</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>Bd. Theodor Pallady 51N, Cladirea C6, Corp A</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>032258</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.metro.ro</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr"/>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>info.online@metro.ro</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>+40 374 115 555</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>8119423</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/metro-group-logistics-romania/</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/METRO.Romania96</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/metro.romania</t>
+        </is>
+      </c>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/MetroRomaniaVideos/</t>
+        </is>
+      </c>
+      <c r="W392" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Alexandru</t>
+        </is>
+      </c>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrei-alexandru-32918922b/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
